--- a/ER_1sub_sem_outliers.xlsx
+++ b/ER_1sub_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>26.68566666666667</v>
+        <v>26.5192</v>
       </c>
       <c r="D2">
-        <v>25.777</v>
+        <v>26.54633333333333</v>
       </c>
       <c r="E2">
-        <v>24.936</v>
+        <v>26.291</v>
       </c>
       <c r="F2">
-        <v>25.655</v>
-      </c>
-      <c r="G2">
-        <v>24.863</v>
+        <v>25.392</v>
       </c>
       <c r="H2">
-        <v>27.482</v>
+        <v>28.0048</v>
+      </c>
+      <c r="I2">
+        <v>27.9872</v>
       </c>
       <c r="J2">
-        <v>23.9965</v>
+        <v>26.87066666666666</v>
+      </c>
+      <c r="K2">
+        <v>27.9882</v>
       </c>
       <c r="L2">
-        <v>25.114</v>
+        <v>27.3515</v>
+      </c>
+      <c r="M2">
+        <v>27.7194</v>
       </c>
     </row>
     <row r="3">
@@ -508,34 +514,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>23.552</v>
+        <v>26.2005</v>
       </c>
       <c r="D4">
-        <v>23.862</v>
+        <v>17.7056</v>
       </c>
       <c r="E4">
-        <v>20.53366666666667</v>
+        <v>20.621</v>
       </c>
       <c r="F4">
-        <v>23.597</v>
+        <v>23.8148</v>
       </c>
       <c r="G4">
-        <v>23.56325</v>
+        <v>24.02033333333334</v>
       </c>
       <c r="H4">
-        <v>20.991</v>
+        <v>24.081</v>
       </c>
       <c r="I4">
-        <v>20.813</v>
+        <v>26.43833333333333</v>
       </c>
       <c r="J4">
-        <v>19.93666666666667</v>
+        <v>23.45533333333333</v>
       </c>
       <c r="K4">
-        <v>19.956</v>
+        <v>25.34416666666667</v>
       </c>
       <c r="L4">
-        <v>10.57525</v>
+        <v>19.02283333333333</v>
+      </c>
+      <c r="M4">
+        <v>23.99233333333333</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +557,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>26.337</v>
+        <v>26.755</v>
       </c>
       <c r="D5">
-        <v>23.91366666666667</v>
+        <v>28.352</v>
       </c>
       <c r="E5">
-        <v>25.5564</v>
+        <v>27.413</v>
       </c>
       <c r="F5">
-        <v>25.98425</v>
+        <v>26.673</v>
       </c>
       <c r="G5">
-        <v>25.7015</v>
+        <v>27.15725</v>
       </c>
       <c r="H5">
-        <v>25.813</v>
+        <v>27.1572</v>
       </c>
       <c r="I5">
-        <v>24.801</v>
+        <v>26.724</v>
       </c>
       <c r="J5">
-        <v>21.668</v>
+        <v>26.4758</v>
+      </c>
+      <c r="K5">
+        <v>25.649</v>
       </c>
       <c r="L5">
-        <v>26.2245</v>
+        <v>25.201</v>
       </c>
       <c r="M5">
-        <v>26.87</v>
+        <v>27.455</v>
       </c>
     </row>
     <row r="6">
@@ -674,34 +686,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>25.4584</v>
+        <v>28.707</v>
+      </c>
+      <c r="D8">
+        <v>24.772</v>
       </c>
       <c r="E8">
-        <v>24.431</v>
+        <v>27.2745</v>
       </c>
       <c r="F8">
-        <v>19.1545</v>
+        <v>25.41533333333333</v>
       </c>
       <c r="G8">
-        <v>20.162</v>
+        <v>24.68</v>
       </c>
       <c r="H8">
-        <v>23.774</v>
+        <v>24.54033333333334</v>
       </c>
       <c r="I8">
-        <v>23.7198</v>
+        <v>24.07475</v>
       </c>
       <c r="J8">
-        <v>20.095</v>
+        <v>21.5518</v>
       </c>
       <c r="K8">
-        <v>19.044</v>
+        <v>19.34766666666667</v>
       </c>
       <c r="L8">
-        <v>21.56</v>
+        <v>18.579</v>
       </c>
       <c r="M8">
-        <v>20.275</v>
+        <v>21.946</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +729,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>27.1885</v>
+        <v>27.006</v>
       </c>
       <c r="D9">
-        <v>23.1295</v>
+        <v>21.077</v>
+      </c>
+      <c r="E9">
+        <v>11.11233333333333</v>
       </c>
       <c r="F9">
-        <v>22.5556</v>
+        <v>15.77683333333333</v>
       </c>
       <c r="G9">
-        <v>24.1695</v>
+        <v>18.0294</v>
       </c>
       <c r="H9">
-        <v>24.96783333333333</v>
+        <v>16.64866666666667</v>
       </c>
       <c r="I9">
-        <v>22.2152</v>
+        <v>11.70666666666667</v>
       </c>
       <c r="J9">
-        <v>25.5235</v>
+        <v>16.7225</v>
       </c>
       <c r="K9">
-        <v>21.7975</v>
+        <v>18.541</v>
       </c>
       <c r="L9">
-        <v>22.953</v>
+        <v>17.1526</v>
       </c>
       <c r="M9">
-        <v>22.461</v>
+        <v>12.4342</v>
       </c>
     </row>
     <row r="10">
@@ -762,6 +780,9 @@
       <c r="E10">
         <v>12.02533333333333</v>
       </c>
+      <c r="F10">
+        <v>8.640000000000001</v>
+      </c>
       <c r="G10">
         <v>10.4558</v>
       </c>
@@ -796,11 +817,17 @@
       <c r="C11">
         <v>23.285</v>
       </c>
+      <c r="D11">
+        <v>11.42466666666667</v>
+      </c>
       <c r="E11">
         <v>7.992166666666666</v>
       </c>
       <c r="F11">
         <v>10.07283333333333</v>
+      </c>
+      <c r="G11">
+        <v>8.685333333333334</v>
       </c>
       <c r="H11">
         <v>5.884166666666666</v>
@@ -874,31 +901,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>21.97233333333334</v>
+        <v>24.0556</v>
+      </c>
+      <c r="D13">
+        <v>20.9335</v>
       </c>
       <c r="E13">
-        <v>22.7325</v>
+        <v>18.0724</v>
+      </c>
+      <c r="F13">
+        <v>18.61283333333333</v>
       </c>
       <c r="G13">
-        <v>21.0495</v>
+        <v>22.6984</v>
       </c>
       <c r="H13">
-        <v>25.339</v>
+        <v>23.90816666666666</v>
       </c>
       <c r="I13">
-        <v>22.964</v>
+        <v>18.9296</v>
       </c>
       <c r="J13">
-        <v>21.6145</v>
+        <v>21.59066666666666</v>
       </c>
       <c r="K13">
-        <v>21.246</v>
+        <v>22.387</v>
       </c>
       <c r="L13">
-        <v>20.0945</v>
+        <v>21.466</v>
       </c>
       <c r="M13">
-        <v>22.255</v>
+        <v>20.24416666666667</v>
       </c>
     </row>
     <row r="14">
@@ -954,37 +987,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>28.4596</v>
+        <v>28.074</v>
       </c>
       <c r="D15">
-        <v>27.15966666666667</v>
+        <v>16.8176</v>
       </c>
       <c r="E15">
-        <v>26.762</v>
+        <v>13.7298</v>
       </c>
       <c r="F15">
-        <v>26.90816666666667</v>
+        <v>15.24733333333333</v>
       </c>
       <c r="G15">
-        <v>27.0604</v>
+        <v>14.5446</v>
       </c>
       <c r="H15">
-        <v>26.3832</v>
+        <v>13.053</v>
       </c>
       <c r="I15">
-        <v>26.2984</v>
+        <v>11.88875</v>
       </c>
       <c r="J15">
-        <v>26.506</v>
+        <v>13.37166666666666</v>
       </c>
       <c r="K15">
-        <v>26.509</v>
+        <v>9.8782</v>
       </c>
       <c r="L15">
-        <v>27.69883333333334</v>
+        <v>16.1105</v>
       </c>
       <c r="M15">
-        <v>25.455</v>
+        <v>13.3244</v>
       </c>
     </row>
     <row r="16">
@@ -1039,6 +1072,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>24.094</v>
+      </c>
+      <c r="D17">
+        <v>21.2698</v>
+      </c>
+      <c r="E17">
+        <v>22.315</v>
+      </c>
+      <c r="F17">
+        <v>17.15133333333333</v>
+      </c>
+      <c r="G17">
+        <v>4.384166666666666</v>
+      </c>
+      <c r="H17">
+        <v>14.3266</v>
+      </c>
+      <c r="I17">
+        <v>12.7485</v>
+      </c>
+      <c r="J17">
+        <v>8.9635</v>
+      </c>
+      <c r="K17">
+        <v>10.0015</v>
+      </c>
+      <c r="L17">
+        <v>13.45283333333333</v>
+      </c>
+      <c r="M17">
+        <v>10.3758</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1993,34 +2059,31 @@
         </is>
       </c>
       <c r="C40">
-        <v>27.93825</v>
+        <v>22.43333333333333</v>
       </c>
       <c r="D40">
-        <v>26.6886</v>
+        <v>21.09416666666667</v>
       </c>
       <c r="E40">
-        <v>26.322</v>
+        <v>23.59266666666667</v>
       </c>
       <c r="F40">
-        <v>26.519</v>
+        <v>20.7648</v>
       </c>
       <c r="G40">
-        <v>24.6075</v>
+        <v>25.05433333333333</v>
       </c>
       <c r="H40">
-        <v>24.9818</v>
+        <v>27.14133333333334</v>
       </c>
       <c r="I40">
-        <v>25.507</v>
+        <v>27.51066666666667</v>
       </c>
       <c r="J40">
-        <v>25.036</v>
+        <v>25.5515</v>
       </c>
       <c r="K40">
-        <v>25.94066666666667</v>
-      </c>
-      <c r="L40">
-        <v>22.6805</v>
+        <v>25.338</v>
       </c>
     </row>
     <row r="41">
